--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run4/epoch_10/per_file_predictions_epoch_10.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run4/epoch_10/per_file_predictions_epoch_10.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="522">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,778 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.2427,0.0083,0.0822,0.6661</t>
-  </si>
-  <si>
-    <t>0.0042,0.0019,0.0016,0.9962</t>
-  </si>
-  <si>
-    <t>0.0906,0.0082,0.0031,0.9513</t>
-  </si>
-  <si>
-    <t>0.0220,0.0045,0.0042,0.9839</t>
-  </si>
-  <si>
-    <t>0.9743,0.0035,0.0006,0.0295</t>
-  </si>
-  <si>
-    <t>0.9718,0.0107,0.0014,0.0186</t>
-  </si>
-  <si>
-    <t>0.9718,0.0113,0.0016,0.0173</t>
-  </si>
-  <si>
-    <t>0.9755,0.0096,0.0013,0.0153</t>
-  </si>
-  <si>
-    <t>0.9776,0.0150,0.0014,0.0111</t>
-  </si>
-  <si>
-    <t>0.9778,0.0139,0.0011,0.0102</t>
-  </si>
-  <si>
-    <t>0.9649,0.0108,0.0011,0.0265</t>
-  </si>
-  <si>
-    <t>0.9553,0.0051,0.0019,0.0459</t>
-  </si>
-  <si>
-    <t>0.3890,0.1509,0.4865,0.0148</t>
-  </si>
-  <si>
-    <t>0.5459,0.0377,0.5204,0.0168</t>
-  </si>
-  <si>
-    <t>0.6063,0.0611,0.4077,0.0095</t>
-  </si>
-  <si>
-    <t>0.4541,0.0274,0.6665,0.0075</t>
-  </si>
-  <si>
-    <t>0.6688,0.2037,0.1611,0.0440</t>
-  </si>
-  <si>
-    <t>0.0745,0.9168,0.0294,0.0029</t>
-  </si>
-  <si>
-    <t>0.0799,0.9271,0.0133,0.0030</t>
-  </si>
-  <si>
-    <t>0.8761,0.1077,0.0215,0.0197</t>
-  </si>
-  <si>
-    <t>0.2452,0.7987,0.0251,0.0061</t>
-  </si>
-  <si>
-    <t>0.0485,0.9550,0.0087,0.0016</t>
-  </si>
-  <si>
-    <t>0.2804,0.0224,0.8293,0.0074</t>
-  </si>
-  <si>
-    <t>0.1731,0.0336,0.8662,0.0150</t>
-  </si>
-  <si>
-    <t>0.0318,0.0114,0.9749,0.0046</t>
-  </si>
-  <si>
-    <t>0.2669,0.0432,0.8024,0.0076</t>
-  </si>
-  <si>
-    <t>0.1135,0.0150,0.9420,0.0039</t>
-  </si>
-  <si>
-    <t>0.1068,0.0131,0.9133,0.0242</t>
-  </si>
-  <si>
-    <t>0.0074,0.0013,0.9951,0.0015</t>
-  </si>
-  <si>
-    <t>0.7572,0.2214,0.0461,0.0094</t>
-  </si>
-  <si>
-    <t>0.6452,0.2263,0.1523,0.0145</t>
-  </si>
-  <si>
-    <t>0.0006,0.0031,0.9987,0.0019</t>
-  </si>
-  <si>
-    <t>0.0457,0.7982,0.3478,0.0029</t>
-  </si>
-  <si>
-    <t>0.7196,0.0408,0.0401,0.1906</t>
-  </si>
-  <si>
-    <t>0.6778,0.0470,0.3987,0.0365</t>
-  </si>
-  <si>
-    <t>0.8329,0.1497,0.0317,0.0197</t>
-  </si>
-  <si>
-    <t>0.2081,0.5381,0.3829,0.0212</t>
-  </si>
-  <si>
-    <t>0.0183,0.6347,0.7852,0.0058</t>
-  </si>
-  <si>
-    <t>0.0279,0.0419,0.9662,0.0079</t>
-  </si>
-  <si>
-    <t>0.0315,0.0270,0.9664,0.0044</t>
-  </si>
-  <si>
-    <t>0.0093,0.0033,0.9806,0.0226</t>
-  </si>
-  <si>
-    <t>0.0150,0.1064,0.9713,0.0032</t>
-  </si>
-  <si>
-    <t>0.0118,0.7866,0.7946,0.0038</t>
-  </si>
-  <si>
-    <t>0.0522,0.0418,0.9573,0.0029</t>
-  </si>
-  <si>
-    <t>0.5161,0.2627,0.2625,0.1585</t>
-  </si>
-  <si>
-    <t>0.0078,0.9679,0.1157,0.0107</t>
-  </si>
-  <si>
-    <t>0.0184,0.9356,0.1469,0.0062</t>
-  </si>
-  <si>
-    <t>0.0082,0.9713,0.0860,0.0076</t>
-  </si>
-  <si>
-    <t>0.0049,0.0879,0.9865,0.0011</t>
-  </si>
-  <si>
-    <t>0.0014,0.0620,0.9959,0.0002</t>
-  </si>
-  <si>
-    <t>0.0391,0.0065,0.9734,0.0040</t>
-  </si>
-  <si>
-    <t>0.0582,0.0037,0.9733,0.0019</t>
-  </si>
-  <si>
-    <t>0.0125,0.0169,0.9895,0.0016</t>
-  </si>
-  <si>
-    <t>0.0980,0.0252,0.9367,0.0035</t>
-  </si>
-  <si>
-    <t>0.9438,0.0249,0.0036,0.0311</t>
-  </si>
-  <si>
-    <t>0.9647,0.0103,0.0043,0.0211</t>
-  </si>
-  <si>
-    <t>0.9404,0.0207,0.0180,0.0264</t>
-  </si>
-  <si>
-    <t>0.0255,0.0119,0.9768,0.0076</t>
-  </si>
-  <si>
-    <t>0.9451,0.0054,0.0026,0.0542</t>
-  </si>
-  <si>
-    <t>0.9743,0.0050,0.0006,0.0256</t>
-  </si>
-  <si>
-    <t>0.9649,0.0315,0.0042,0.0094</t>
-  </si>
-  <si>
-    <t>0.0020,0.8865,0.8658,0.0006</t>
-  </si>
-  <si>
-    <t>0.0098,0.0594,0.9807,0.0012</t>
-  </si>
-  <si>
-    <t>0.0073,0.0050,0.9932,0.0015</t>
-  </si>
-  <si>
-    <t>0.0032,0.8640,0.8966,0.0014</t>
-  </si>
-  <si>
-    <t>0.0020,0.0015,0.9968,0.0026</t>
-  </si>
-  <si>
-    <t>0.1028,0.8622,0.0366,0.0030</t>
-  </si>
-  <si>
-    <t>0.0362,0.9598,0.0023,0.0015</t>
-  </si>
-  <si>
-    <t>0.7256,0.1406,0.1438,0.0267</t>
-  </si>
-  <si>
-    <t>0.6253,0.1664,0.2673,0.0532</t>
-  </si>
-  <si>
-    <t>0.0051,0.0451,0.9923,0.0011</t>
-  </si>
-  <si>
-    <t>0.0069,0.7499,0.8996,0.0024</t>
-  </si>
-  <si>
-    <t>0.0051,0.8292,0.8565,0.0012</t>
-  </si>
-  <si>
-    <t>0.0039,0.9346,0.6633,0.0014</t>
-  </si>
-  <si>
-    <t>0.0048,0.7967,0.8833,0.0021</t>
-  </si>
-  <si>
-    <t>0.0848,0.0031,0.0743,0.8556</t>
-  </si>
-  <si>
-    <t>0.0009,0.0005,0.0026,0.9981</t>
-  </si>
-  <si>
-    <t>0.0037,0.0013,0.0080,0.9939</t>
-  </si>
-  <si>
-    <t>0.0070,0.0023,0.0144,0.9891</t>
-  </si>
-  <si>
-    <t>0.0041,0.0010,0.0102,0.9928</t>
-  </si>
-  <si>
-    <t>0.0033,0.0007,0.0457,0.9846</t>
-  </si>
-  <si>
-    <t>0.0024,0.8592,0.9022,0.0008</t>
-  </si>
-  <si>
-    <t>0.0009,0.6800,0.9830,0.0003</t>
-  </si>
-  <si>
-    <t>0.0530,0.4197,0.7854,0.0067</t>
-  </si>
-  <si>
-    <t>0.0101,0.2770,0.9628,0.0034</t>
-  </si>
-  <si>
-    <t>0.0023,0.8266,0.9298,0.0008</t>
-  </si>
-  <si>
-    <t>0.0063,0.7134,0.9103,0.0026</t>
-  </si>
-  <si>
-    <t>0.9735,0.0131,0.0020,0.0145</t>
-  </si>
-  <si>
-    <t>0.9772,0.0146,0.0016,0.0096</t>
-  </si>
-  <si>
-    <t>0.9708,0.0191,0.0019,0.0117</t>
-  </si>
-  <si>
-    <t>0.9745,0.0106,0.0007,0.0177</t>
-  </si>
-  <si>
-    <t>0.9331,0.0119,0.0045,0.0640</t>
-  </si>
-  <si>
-    <t>0.9696,0.0131,0.0017,0.0172</t>
-  </si>
-  <si>
-    <t>0.9554,0.0055,0.0021,0.0444</t>
-  </si>
-  <si>
-    <t>0.9775,0.0195,0.0019,0.0079</t>
-  </si>
-  <si>
-    <t>0.9810,0.0038,0.0009,0.0168</t>
-  </si>
-  <si>
-    <t>0.9795,0.0069,0.0023,0.0120</t>
-  </si>
-  <si>
-    <t>0.9664,0.0047,0.0007,0.0361</t>
-  </si>
-  <si>
-    <t>0.9692,0.0041,0.0018,0.0306</t>
-  </si>
-  <si>
-    <t>0.9767,0.0036,0.0008,0.0225</t>
-  </si>
-  <si>
-    <t>0.9658,0.0078,0.0020,0.0281</t>
-  </si>
-  <si>
-    <t>0.9459,0.0031,0.0006,0.0807</t>
-  </si>
-  <si>
-    <t>0.9737,0.0041,0.0006,0.0244</t>
-  </si>
-  <si>
-    <t>0.0059,0.0029,0.9956,0.0010</t>
-  </si>
-  <si>
-    <t>0.2973,0.0198,0.8098,0.0068</t>
-  </si>
-  <si>
-    <t>0.6909,0.0211,0.2032,0.0795</t>
-  </si>
-  <si>
-    <t>0.0684,0.0067,0.9618,0.0046</t>
-  </si>
-  <si>
-    <t>0.1647,0.8619,0.0205,0.0066</t>
-  </si>
-  <si>
-    <t>0.1702,0.8498,0.0228,0.0042</t>
-  </si>
-  <si>
-    <t>0.4472,0.6398,0.0186,0.0095</t>
-  </si>
-  <si>
-    <t>0.8395,0.1752,0.0247,0.0136</t>
-  </si>
-  <si>
-    <t>0.1798,0.8475,0.0194,0.0056</t>
-  </si>
-  <si>
-    <t>0.0945,0.9210,0.0084,0.0044</t>
-  </si>
-  <si>
-    <t>0.8339,0.1877,0.0204,0.0118</t>
-  </si>
-  <si>
-    <t>0.5307,0.1194,0.3824,0.0635</t>
-  </si>
-  <si>
-    <t>0.1232,0.0251,0.9306,0.0042</t>
-  </si>
-  <si>
-    <t>0.5819,0.1314,0.2497,0.0145</t>
-  </si>
-  <si>
-    <t>0.6703,0.0412,0.3539,0.0215</t>
-  </si>
-  <si>
-    <t>0.3349,0.1321,0.1640,0.4931</t>
-  </si>
-  <si>
-    <t>0.0029,0.9916,0.0160,0.0020</t>
-  </si>
-  <si>
-    <t>0.0020,0.9936,0.0136,0.0025</t>
-  </si>
-  <si>
-    <t>0.0576,0.9298,0.0153,0.0100</t>
-  </si>
-  <si>
-    <t>0.0030,0.9866,0.0788,0.0026</t>
-  </si>
-  <si>
-    <t>0.0399,0.9344,0.0896,0.0029</t>
-  </si>
-  <si>
-    <t>0.8558,0.1386,0.0347,0.0143</t>
-  </si>
-  <si>
-    <t>0.8379,0.1620,0.0310,0.0114</t>
-  </si>
-  <si>
-    <t>0.9516,0.0182,0.0049,0.0261</t>
-  </si>
-  <si>
-    <t>0.9688,0.0059,0.0020,0.0220</t>
-  </si>
-  <si>
-    <t>0.8867,0.0037,0.0029,0.1448</t>
-  </si>
-  <si>
-    <t>0.9132,0.0051,0.0020,0.1072</t>
-  </si>
-  <si>
-    <t>0.9414,0.0020,0.0010,0.0830</t>
-  </si>
-  <si>
-    <t>0.8488,0.0112,0.0289,0.0910</t>
-  </si>
-  <si>
-    <t>0.9059,0.0087,0.0057,0.0859</t>
-  </si>
-  <si>
-    <t>0.8900,0.0040,0.0025,0.1327</t>
-  </si>
-  <si>
-    <t>0.0078,0.4256,0.9421,0.0016</t>
-  </si>
-  <si>
-    <t>0.0082,0.4359,0.9461,0.0015</t>
-  </si>
-  <si>
-    <t>0.0080,0.0762,0.9828,0.0017</t>
-  </si>
-  <si>
-    <t>0.0653,0.0333,0.9499,0.0026</t>
-  </si>
-  <si>
-    <t>0.8200,0.0292,0.1815,0.0087</t>
-  </si>
-  <si>
-    <t>0.7107,0.0926,0.1141,0.0567</t>
-  </si>
-  <si>
-    <t>0.6049,0.0134,0.5009,0.0211</t>
-  </si>
-  <si>
-    <t>0.5330,0.2522,0.2516,0.0363</t>
-  </si>
-  <si>
-    <t>0.0186,0.0029,0.0076,0.9838</t>
-  </si>
-  <si>
-    <t>0.0003,0.0004,0.0072,0.9982</t>
-  </si>
-  <si>
-    <t>0.0012,0.0007,0.0183,0.9940</t>
-  </si>
-  <si>
-    <t>0.0051,0.0006,0.0124,0.9905</t>
-  </si>
-  <si>
-    <t>0.0027,0.8519,0.8969,0.0018</t>
-  </si>
-  <si>
-    <t>0.9452,0.0066,0.0020,0.0552</t>
-  </si>
-  <si>
-    <t>0.8236,0.2094,0.0111,0.0222</t>
-  </si>
-  <si>
-    <t>0.9266,0.0063,0.0047,0.0650</t>
-  </si>
-  <si>
-    <t>0.8847,0.0926,0.0332,0.0136</t>
-  </si>
-  <si>
-    <t>0.8590,0.0060,0.0087,0.1282</t>
-  </si>
-  <si>
-    <t>0.1178,0.0078,0.0306,0.9032</t>
-  </si>
-  <si>
-    <t>0.5508,0.0023,0.0119,0.4447</t>
-  </si>
-  <si>
-    <t>0.0391,0.0430,0.9509,0.0080</t>
-  </si>
-  <si>
-    <t>0.1423,0.0033,0.0508,0.8027</t>
-  </si>
-  <si>
-    <t>0.4596,0.0036,0.0359,0.4967</t>
-  </si>
-  <si>
-    <t>0.4562,0.3453,0.2295,0.0252</t>
-  </si>
-  <si>
-    <t>0.8838,0.1065,0.0190,0.0146</t>
-  </si>
-  <si>
-    <t>0.8556,0.0355,0.0414,0.0533</t>
-  </si>
-  <si>
-    <t>0.2298,0.7038,0.0741,0.0709</t>
-  </si>
-  <si>
-    <t>0.7790,0.1126,0.1165,0.0151</t>
-  </si>
-  <si>
-    <t>0.7758,0.1264,0.0951,0.0267</t>
-  </si>
-  <si>
-    <t>0.9713,0.0055,0.0018,0.0205</t>
-  </si>
-  <si>
-    <t>0.8983,0.0026,0.0009,0.1701</t>
-  </si>
-  <si>
-    <t>0.9415,0.0080,0.0035,0.0501</t>
-  </si>
-  <si>
-    <t>0.8932,0.0062,0.0051,0.1079</t>
-  </si>
-  <si>
-    <t>0.9282,0.0036,0.0046,0.0675</t>
-  </si>
-  <si>
-    <t>0.9735,0.0057,0.0017,0.0171</t>
-  </si>
-  <si>
-    <t>0.9559,0.0039,0.0038,0.0341</t>
-  </si>
-  <si>
-    <t>0.8978,0.0077,0.0015,0.1342</t>
-  </si>
-  <si>
-    <t>0.7335,0.2513,0.0499,0.0275</t>
-  </si>
-  <si>
-    <t>0.9419,0.0458,0.0035,0.0189</t>
-  </si>
-  <si>
-    <t>0.9042,0.0907,0.0133,0.0141</t>
-  </si>
-  <si>
-    <t>0.6909,0.1279,0.2377,0.0304</t>
-  </si>
-  <si>
-    <t>0.9294,0.0328,0.0018,0.0368</t>
-  </si>
-  <si>
-    <t>0.9494,0.0347,0.0067,0.0176</t>
-  </si>
-  <si>
-    <t>0.9377,0.0160,0.0040,0.0383</t>
-  </si>
-  <si>
-    <t>0.9294,0.0607,0.0078,0.0152</t>
-  </si>
-  <si>
-    <t>0.0031,0.0524,0.9951,0.0009</t>
-  </si>
-  <si>
-    <t>0.9605,0.0116,0.0055,0.0182</t>
-  </si>
-  <si>
-    <t>0.0012,0.0015,0.9988,0.0006</t>
-  </si>
-  <si>
-    <t>0.0215,0.0108,0.9790,0.0053</t>
-  </si>
-  <si>
-    <t>0.0240,0.0084,0.9815,0.0031</t>
-  </si>
-  <si>
-    <t>0.0090,0.1688,0.9754,0.0015</t>
-  </si>
-  <si>
-    <t>0.0463,0.0076,0.9707,0.0028</t>
-  </si>
-  <si>
-    <t>0.0038,0.0037,0.9964,0.0009</t>
-  </si>
-  <si>
-    <t>0.0073,0.0017,0.9950,0.0011</t>
-  </si>
-  <si>
-    <t>0.3886,0.0943,0.5820,0.0258</t>
-  </si>
-  <si>
-    <t>0.0871,0.0274,0.9393,0.0084</t>
-  </si>
-  <si>
-    <t>0.4370,0.2057,0.2841,0.0105</t>
-  </si>
-  <si>
-    <t>0.1427,0.2457,0.6457,0.0041</t>
-  </si>
-  <si>
-    <t>0.1686,0.1727,0.7339,0.0087</t>
-  </si>
-  <si>
-    <t>0.4363,0.0439,0.6554,0.0141</t>
-  </si>
-  <si>
-    <t>0.5876,0.0533,0.4185,0.0337</t>
-  </si>
-  <si>
-    <t>0.2845,0.1553,0.6113,0.0130</t>
-  </si>
-  <si>
-    <t>0.9314,0.0770,0.0091,0.0064</t>
-  </si>
-  <si>
-    <t>0.7839,0.3264,0.0063,0.0053</t>
-  </si>
-  <si>
-    <t>0.8218,0.2270,0.0128,0.0154</t>
-  </si>
-  <si>
-    <t>0.9667,0.0304,0.0045,0.0093</t>
-  </si>
-  <si>
-    <t>0.8879,0.1917,0.0052,0.0065</t>
-  </si>
-  <si>
-    <t>0.5607,0.1396,0.3561,0.0434</t>
-  </si>
-  <si>
-    <t>0.7982,0.0190,0.2098,0.0187</t>
-  </si>
-  <si>
-    <t>0.5331,0.0339,0.1719,0.2387</t>
-  </si>
-  <si>
-    <t>0.5878,0.0438,0.4539,0.0155</t>
-  </si>
-  <si>
-    <t>0.7233,0.0447,0.2582,0.0323</t>
-  </si>
-  <si>
-    <t>0.0081,0.0065,0.9920,0.0028</t>
-  </si>
-  <si>
-    <t>0.0319,0.0259,0.9658,0.0069</t>
-  </si>
-  <si>
-    <t>0.0247,0.0135,0.9689,0.0095</t>
-  </si>
-  <si>
-    <t>0.0990,0.0780,0.8991,0.0061</t>
-  </si>
-  <si>
-    <t>0.0133,0.0135,0.9841,0.0033</t>
-  </si>
-  <si>
-    <t>0.9615,0.0136,0.0036,0.0236</t>
-  </si>
-  <si>
-    <t>0.9723,0.0070,0.0033,0.0170</t>
-  </si>
-  <si>
-    <t>0.9808,0.0112,0.0012,0.0107</t>
-  </si>
-  <si>
-    <t>0.9824,0.0076,0.0012,0.0094</t>
-  </si>
-  <si>
-    <t>0.9462,0.0279,0.0076,0.0275</t>
-  </si>
-  <si>
-    <t>0.9775,0.0177,0.0028,0.0079</t>
-  </si>
-  <si>
-    <t>0.9645,0.0062,0.0025,0.0302</t>
-  </si>
-  <si>
-    <t>0.9569,0.0042,0.0017,0.0454</t>
-  </si>
-  <si>
-    <t>0.1455,0.0198,0.9232,0.0050</t>
-  </si>
-  <si>
-    <t>0.2359,0.4061,0.3400,0.0057</t>
-  </si>
-  <si>
-    <t>0.7635,0.0087,0.2060,0.0388</t>
-  </si>
-  <si>
-    <t>0.0105,0.0096,0.9925,0.0007</t>
-  </si>
-  <si>
-    <t>0.0007,0.0015,0.9990,0.0007</t>
-  </si>
-  <si>
-    <t>0.0171,0.0312,0.9805,0.0025</t>
-  </si>
-  <si>
-    <t>0.0014,0.0016,0.9989,0.0003</t>
-  </si>
-  <si>
-    <t>0.0658,0.0375,0.9453,0.0034</t>
-  </si>
-  <si>
-    <t>0.0024,0.0021,0.9982,0.0004</t>
-  </si>
-  <si>
-    <t>0.0086,0.0056,0.9938,0.0007</t>
-  </si>
-  <si>
-    <t>0.1981,0.0688,0.8246,0.0133</t>
-  </si>
-  <si>
-    <t>0.5079,0.0255,0.5366,0.0349</t>
-  </si>
-  <si>
-    <t>0.6415,0.0458,0.3483,0.0195</t>
-  </si>
-  <si>
-    <t>0.7478,0.0607,0.1442,0.0466</t>
-  </si>
-  <si>
-    <t>0.9387,0.0285,0.0027,0.0348</t>
-  </si>
-  <si>
-    <t>0.9832,0.0087,0.0007,0.0085</t>
-  </si>
-  <si>
-    <t>0.9636,0.0115,0.0012,0.0299</t>
-  </si>
-  <si>
-    <t>0.9652,0.0113,0.0062,0.0154</t>
-  </si>
-  <si>
-    <t>0.9206,0.0072,0.0022,0.0793</t>
-  </si>
-  <si>
-    <t>0.9589,0.0266,0.0048,0.0144</t>
-  </si>
-  <si>
-    <t>0.9802,0.0069,0.0008,0.0133</t>
-  </si>
-  <si>
-    <t>0.9664,0.0093,0.0017,0.0246</t>
-  </si>
-  <si>
-    <t>0.1068,0.0299,0.9361,0.0025</t>
-  </si>
-  <si>
-    <t>0.0116,0.0236,0.9877,0.0015</t>
-  </si>
-  <si>
-    <t>0.0239,0.0227,0.9730,0.0055</t>
-  </si>
-  <si>
-    <t>0.3964,0.0249,0.7306,0.0119</t>
-  </si>
-  <si>
-    <t>0.0534,0.0056,0.9731,0.0024</t>
-  </si>
-  <si>
-    <t>0.0457,0.0093,0.8961,0.1248</t>
-  </si>
-  <si>
-    <t>0.1700,0.0112,0.8775,0.0248</t>
-  </si>
-  <si>
-    <t>0.0139,0.0150,0.9665,0.0312</t>
-  </si>
-  <si>
-    <t>0.2815,0.0074,0.0247,0.7331</t>
-  </si>
-  <si>
-    <t>0.0600,0.0086,0.0086,0.9608</t>
-  </si>
-  <si>
-    <t>0.0218,0.0015,0.0134,0.9745</t>
-  </si>
-  <si>
-    <t>0.0008,0.0005,0.0023,0.9984</t>
-  </si>
-  <si>
-    <t>0.0023,0.0006,0.0031,0.9963</t>
-  </si>
-  <si>
-    <t>0.6369,0.0723,0.0842,0.2405</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0.4652,0.0731,0.0749,0.4342</t>
+  </si>
+  <si>
+    <t>0.0045,0.0011,0.0029,0.9951</t>
+  </si>
+  <si>
+    <t>0.2267,0.0053,0.0056,0.8619</t>
+  </si>
+  <si>
+    <t>0.0455,0.0079,0.0136,0.9662</t>
+  </si>
+  <si>
+    <t>0.9770,0.0066,0.0015,0.0160</t>
+  </si>
+  <si>
+    <t>0.9810,0.0085,0.0004,0.0120</t>
+  </si>
+  <si>
+    <t>0.9733,0.0110,0.0027,0.0136</t>
+  </si>
+  <si>
+    <t>0.9697,0.0076,0.0015,0.0249</t>
+  </si>
+  <si>
+    <t>0.9754,0.0034,0.0005,0.0276</t>
+  </si>
+  <si>
+    <t>0.9846,0.0039,0.0004,0.0137</t>
+  </si>
+  <si>
+    <t>0.9742,0.0070,0.0011,0.0212</t>
+  </si>
+  <si>
+    <t>0.9568,0.0045,0.0013,0.0494</t>
+  </si>
+  <si>
+    <t>0.6537,0.1174,0.2430,0.0171</t>
+  </si>
+  <si>
+    <t>0.0997,0.0370,0.9321,0.0071</t>
+  </si>
+  <si>
+    <t>0.2623,0.1151,0.6107,0.0021</t>
+  </si>
+  <si>
+    <t>0.0811,0.0323,0.9408,0.0037</t>
+  </si>
+  <si>
+    <t>0.4434,0.0654,0.6362,0.0250</t>
+  </si>
+  <si>
+    <t>0.0310,0.9647,0.0115,0.0015</t>
+  </si>
+  <si>
+    <t>0.2015,0.8362,0.0163,0.0028</t>
+  </si>
+  <si>
+    <t>0.8688,0.1092,0.0359,0.0174</t>
+  </si>
+  <si>
+    <t>0.3568,0.6908,0.0319,0.0071</t>
+  </si>
+  <si>
+    <t>0.0412,0.9605,0.0081,0.0010</t>
+  </si>
+  <si>
+    <t>0.5691,0.0204,0.5190,0.0178</t>
+  </si>
+  <si>
+    <t>0.4316,0.0318,0.6742,0.0108</t>
+  </si>
+  <si>
+    <t>0.0123,0.0026,0.9915,0.0019</t>
+  </si>
+  <si>
+    <t>0.4077,0.0461,0.6547,0.0139</t>
+  </si>
+  <si>
+    <t>0.0206,0.0031,0.9874,0.0030</t>
+  </si>
+  <si>
+    <t>0.1119,0.0098,0.9488,0.0032</t>
+  </si>
+  <si>
+    <t>0.0046,0.0007,0.9961,0.0017</t>
+  </si>
+  <si>
+    <t>0.8609,0.0897,0.0542,0.0070</t>
+  </si>
+  <si>
+    <t>0.8057,0.1042,0.0924,0.0169</t>
+  </si>
+  <si>
+    <t>0.0038,0.0047,0.9943,0.0044</t>
+  </si>
+  <si>
+    <t>0.0306,0.7752,0.4811,0.0032</t>
+  </si>
+  <si>
+    <t>0.7877,0.0235,0.0322,0.1332</t>
+  </si>
+  <si>
+    <t>0.1759,0.0166,0.8925,0.0246</t>
+  </si>
+  <si>
+    <t>0.8899,0.0830,0.0357,0.0200</t>
+  </si>
+  <si>
+    <t>0.1772,0.6963,0.2232,0.0279</t>
+  </si>
+  <si>
+    <t>0.0324,0.4536,0.8254,0.0063</t>
+  </si>
+  <si>
+    <t>0.0267,0.0646,0.9607,0.0063</t>
+  </si>
+  <si>
+    <t>0.0236,0.0363,0.9581,0.0140</t>
+  </si>
+  <si>
+    <t>0.0214,0.0084,0.9606,0.0402</t>
+  </si>
+  <si>
+    <t>0.0396,0.1088,0.9493,0.0030</t>
+  </si>
+  <si>
+    <t>0.0055,0.9343,0.5314,0.0021</t>
+  </si>
+  <si>
+    <t>0.0535,0.0129,0.9635,0.0043</t>
+  </si>
+  <si>
+    <t>0.3022,0.1883,0.2118,0.5193</t>
+  </si>
+  <si>
+    <t>0.0209,0.9603,0.0264,0.0051</t>
+  </si>
+  <si>
+    <t>0.0070,0.9633,0.1459,0.0113</t>
+  </si>
+  <si>
+    <t>0.0014,0.9901,0.1373,0.0020</t>
+  </si>
+  <si>
+    <t>0.0024,0.0618,0.9942,0.0005</t>
+  </si>
+  <si>
+    <t>0.0023,0.0190,0.9967,0.0005</t>
+  </si>
+  <si>
+    <t>0.0842,0.0031,0.9422,0.0139</t>
+  </si>
+  <si>
+    <t>0.0148,0.0018,0.9885,0.0034</t>
+  </si>
+  <si>
+    <t>0.0044,0.0065,0.9952,0.0017</t>
+  </si>
+  <si>
+    <t>0.1272,0.0175,0.9315,0.0049</t>
+  </si>
+  <si>
+    <t>0.9642,0.0244,0.0029,0.0122</t>
+  </si>
+  <si>
+    <t>0.9354,0.0065,0.0099,0.0438</t>
+  </si>
+  <si>
+    <t>0.9461,0.0266,0.0345,0.0142</t>
+  </si>
+  <si>
+    <t>0.0404,0.0114,0.9711,0.0086</t>
+  </si>
+  <si>
+    <t>0.9489,0.0056,0.0020,0.0527</t>
+  </si>
+  <si>
+    <t>0.9814,0.0074,0.0010,0.0107</t>
+  </si>
+  <si>
+    <t>0.9732,0.0099,0.0015,0.0169</t>
+  </si>
+  <si>
+    <t>0.0052,0.9068,0.6946,0.0021</t>
+  </si>
+  <si>
+    <t>0.0357,0.0509,0.9657,0.0019</t>
+  </si>
+  <si>
+    <t>0.0044,0.0048,0.9950,0.0012</t>
+  </si>
+  <si>
+    <t>0.0020,0.7439,0.9619,0.0008</t>
+  </si>
+  <si>
+    <t>0.0015,0.0009,0.9981,0.0011</t>
+  </si>
+  <si>
+    <t>0.1606,0.7922,0.0566,0.0076</t>
+  </si>
+  <si>
+    <t>0.0149,0.9816,0.0017,0.0007</t>
+  </si>
+  <si>
+    <t>0.7188,0.0657,0.2963,0.0282</t>
+  </si>
+  <si>
+    <t>0.5444,0.2872,0.2021,0.0164</t>
+  </si>
+  <si>
+    <t>0.0116,0.0448,0.9862,0.0018</t>
+  </si>
+  <si>
+    <t>0.0081,0.8506,0.7873,0.0038</t>
+  </si>
+  <si>
+    <t>0.0140,0.6869,0.8388,0.0054</t>
+  </si>
+  <si>
+    <t>0.0038,0.9091,0.8028,0.0016</t>
+  </si>
+  <si>
+    <t>0.0085,0.7579,0.8569,0.0026</t>
+  </si>
+  <si>
+    <t>0.0603,0.0020,0.0323,0.9240</t>
+  </si>
+  <si>
+    <t>0.0017,0.0014,0.0035,0.9969</t>
+  </si>
+  <si>
+    <t>0.0048,0.0005,0.0052,0.9931</t>
+  </si>
+  <si>
+    <t>0.0054,0.0005,0.0079,0.9917</t>
+  </si>
+  <si>
+    <t>0.0071,0.0021,0.0154,0.9884</t>
+  </si>
+  <si>
+    <t>0.0016,0.0006,0.0128,0.9949</t>
+  </si>
+  <si>
+    <t>0.0045,0.8310,0.8616,0.0010</t>
+  </si>
+  <si>
+    <t>0.0022,0.4448,0.9817,0.0008</t>
+  </si>
+  <si>
+    <t>0.0201,0.7549,0.7014,0.0100</t>
+  </si>
+  <si>
+    <t>0.0158,0.3502,0.9335,0.0038</t>
+  </si>
+  <si>
+    <t>0.0057,0.8027,0.8695,0.0013</t>
+  </si>
+  <si>
+    <t>0.0107,0.7543,0.8232,0.0035</t>
+  </si>
+  <si>
+    <t>0.9798,0.0104,0.0012,0.0103</t>
+  </si>
+  <si>
+    <t>0.9718,0.0209,0.0047,0.0079</t>
+  </si>
+  <si>
+    <t>0.9736,0.0222,0.0031,0.0070</t>
+  </si>
+  <si>
+    <t>0.9642,0.0032,0.0004,0.0489</t>
+  </si>
+  <si>
+    <t>0.9644,0.0098,0.0024,0.0259</t>
+  </si>
+  <si>
+    <t>0.9780,0.0118,0.0010,0.0120</t>
+  </si>
+  <si>
+    <t>0.9712,0.0038,0.0005,0.0340</t>
+  </si>
+  <si>
+    <t>0.9825,0.0117,0.0017,0.0095</t>
+  </si>
+  <si>
+    <t>0.9667,0.0056,0.0016,0.0294</t>
+  </si>
+  <si>
+    <t>0.9830,0.0036,0.0005,0.0155</t>
+  </si>
+  <si>
+    <t>0.9590,0.0024,0.0006,0.0609</t>
+  </si>
+  <si>
+    <t>0.9873,0.0035,0.0005,0.0111</t>
+  </si>
+  <si>
+    <t>0.9679,0.0118,0.0021,0.0195</t>
+  </si>
+  <si>
+    <t>0.9875,0.0060,0.0004,0.0075</t>
+  </si>
+  <si>
+    <t>0.9768,0.0043,0.0014,0.0198</t>
+  </si>
+  <si>
+    <t>0.9722,0.0039,0.0013,0.0279</t>
+  </si>
+  <si>
+    <t>0.0083,0.0011,0.9950,0.0014</t>
+  </si>
+  <si>
+    <t>0.2128,0.0240,0.8662,0.0096</t>
+  </si>
+  <si>
+    <t>0.7794,0.0488,0.1587,0.0257</t>
+  </si>
+  <si>
+    <t>0.0391,0.0039,0.9798,0.0030</t>
+  </si>
+  <si>
+    <t>0.2003,0.8404,0.0181,0.0083</t>
+  </si>
+  <si>
+    <t>0.1225,0.8697,0.0358,0.0039</t>
+  </si>
+  <si>
+    <t>0.5404,0.5675,0.0128,0.0045</t>
+  </si>
+  <si>
+    <t>0.4284,0.6582,0.0184,0.0113</t>
+  </si>
+  <si>
+    <t>0.1853,0.8511,0.0193,0.0054</t>
+  </si>
+  <si>
+    <t>0.1550,0.8887,0.0054,0.0020</t>
+  </si>
+  <si>
+    <t>0.9345,0.0537,0.0095,0.0159</t>
+  </si>
+  <si>
+    <t>0.5337,0.1085,0.2452,0.1604</t>
+  </si>
+  <si>
+    <t>0.1149,0.0154,0.9226,0.0102</t>
+  </si>
+  <si>
+    <t>0.6736,0.0677,0.2551,0.0224</t>
+  </si>
+  <si>
+    <t>0.7267,0.0460,0.2534,0.0111</t>
+  </si>
+  <si>
+    <t>0.4139,0.0300,0.2283,0.3668</t>
+  </si>
+  <si>
+    <t>0.0014,0.9947,0.0170,0.0014</t>
+  </si>
+  <si>
+    <t>0.0094,0.9669,0.0591,0.0159</t>
+  </si>
+  <si>
+    <t>0.0565,0.9222,0.0284,0.0176</t>
+  </si>
+  <si>
+    <t>0.0038,0.9886,0.0283,0.0012</t>
+  </si>
+  <si>
+    <t>0.0731,0.9194,0.0408,0.0030</t>
+  </si>
+  <si>
+    <t>0.8663,0.1138,0.0350,0.0219</t>
+  </si>
+  <si>
+    <t>0.8527,0.1572,0.0231,0.0072</t>
+  </si>
+  <si>
+    <t>0.9470,0.0045,0.0034,0.0468</t>
+  </si>
+  <si>
+    <t>0.9516,0.0042,0.0019,0.0472</t>
+  </si>
+  <si>
+    <t>0.9466,0.0076,0.0015,0.0573</t>
+  </si>
+  <si>
+    <t>0.9576,0.0077,0.0040,0.0280</t>
+  </si>
+  <si>
+    <t>0.9787,0.0034,0.0004,0.0178</t>
+  </si>
+  <si>
+    <t>0.8874,0.0067,0.0137,0.0746</t>
+  </si>
+  <si>
+    <t>0.9658,0.0090,0.0018,0.0243</t>
+  </si>
+  <si>
+    <t>0.9081,0.0135,0.0078,0.0695</t>
+  </si>
+  <si>
+    <t>0.0111,0.3965,0.9453,0.0022</t>
+  </si>
+  <si>
+    <t>0.0249,0.1178,0.9546,0.0025</t>
+  </si>
+  <si>
+    <t>0.0028,0.0239,0.9956,0.0006</t>
+  </si>
+  <si>
+    <t>0.0367,0.0697,0.9535,0.0025</t>
+  </si>
+  <si>
+    <t>0.8298,0.0437,0.0987,0.0187</t>
+  </si>
+  <si>
+    <t>0.6763,0.0965,0.1884,0.0563</t>
+  </si>
+  <si>
+    <t>0.0536,0.0124,0.9628,0.0097</t>
+  </si>
+  <si>
+    <t>0.6667,0.1461,0.1782,0.0561</t>
+  </si>
+  <si>
+    <t>0.0570,0.0014,0.0181,0.9393</t>
+  </si>
+  <si>
+    <t>0.0000,0.0003,0.0063,0.9992</t>
+  </si>
+  <si>
+    <t>0.0026,0.0013,0.0079,0.9949</t>
+  </si>
+  <si>
+    <t>0.0022,0.0012,0.0071,0.9954</t>
+  </si>
+  <si>
+    <t>0.0038,0.8449,0.8706,0.0023</t>
+  </si>
+  <si>
+    <t>0.9580,0.0082,0.0036,0.0300</t>
+  </si>
+  <si>
+    <t>0.7874,0.2607,0.0123,0.0216</t>
+  </si>
+  <si>
+    <t>0.9137,0.0082,0.0070,0.0771</t>
+  </si>
+  <si>
+    <t>0.9053,0.0759,0.0151,0.0245</t>
+  </si>
+  <si>
+    <t>0.9354,0.0086,0.0107,0.0389</t>
+  </si>
+  <si>
+    <t>0.0425,0.0048,0.0446,0.9449</t>
+  </si>
+  <si>
+    <t>0.6014,0.0070,0.0097,0.4579</t>
+  </si>
+  <si>
+    <t>0.0340,0.0589,0.9459,0.0135</t>
+  </si>
+  <si>
+    <t>0.1725,0.0045,0.0253,0.8561</t>
+  </si>
+  <si>
+    <t>0.1494,0.0020,0.0237,0.8445</t>
+  </si>
+  <si>
+    <t>0.5772,0.2937,0.1610,0.0310</t>
+  </si>
+  <si>
+    <t>0.7409,0.0173,0.0864,0.1249</t>
+  </si>
+  <si>
+    <t>0.8784,0.0686,0.0503,0.0093</t>
+  </si>
+  <si>
+    <t>0.5493,0.3795,0.0644,0.0541</t>
+  </si>
+  <si>
+    <t>0.8632,0.0649,0.0740,0.0177</t>
+  </si>
+  <si>
+    <t>0.7066,0.1751,0.1520,0.0371</t>
+  </si>
+  <si>
+    <t>0.9557,0.0086,0.0018,0.0394</t>
+  </si>
+  <si>
+    <t>0.9122,0.0109,0.0016,0.1001</t>
+  </si>
+  <si>
+    <t>0.9544,0.0056,0.0049,0.0389</t>
+  </si>
+  <si>
+    <t>0.7851,0.0033,0.0032,0.2830</t>
+  </si>
+  <si>
+    <t>0.9479,0.0060,0.0046,0.0390</t>
+  </si>
+  <si>
+    <t>0.9756,0.0054,0.0014,0.0198</t>
+  </si>
+  <si>
+    <t>0.9123,0.0037,0.0025,0.1047</t>
+  </si>
+  <si>
+    <t>0.9549,0.0075,0.0014,0.0393</t>
+  </si>
+  <si>
+    <t>0.7272,0.2604,0.0397,0.0263</t>
+  </si>
+  <si>
+    <t>0.9309,0.0550,0.0091,0.0151</t>
+  </si>
+  <si>
+    <t>0.9114,0.0725,0.0230,0.0123</t>
+  </si>
+  <si>
+    <t>0.4947,0.4353,0.1637,0.0315</t>
+  </si>
+  <si>
+    <t>0.9081,0.0662,0.0030,0.0363</t>
+  </si>
+  <si>
+    <t>0.9375,0.0158,0.0102,0.0338</t>
+  </si>
+  <si>
+    <t>0.9176,0.0213,0.0079,0.0517</t>
+  </si>
+  <si>
+    <t>0.9224,0.0798,0.0104,0.0129</t>
+  </si>
+  <si>
+    <t>0.0035,0.0192,0.9963,0.0007</t>
+  </si>
+  <si>
+    <t>0.9420,0.0096,0.0104,0.0337</t>
+  </si>
+  <si>
+    <t>0.0013,0.0034,0.9982,0.0008</t>
+  </si>
+  <si>
+    <t>0.0039,0.0077,0.9958,0.0009</t>
+  </si>
+  <si>
+    <t>0.0509,0.0050,0.9684,0.0058</t>
+  </si>
+  <si>
+    <t>0.0196,0.1080,0.9682,0.0014</t>
+  </si>
+  <si>
+    <t>0.0590,0.0098,0.9640,0.0029</t>
+  </si>
+  <si>
+    <t>0.0088,0.0020,0.9939,0.0015</t>
+  </si>
+  <si>
+    <t>0.0321,0.0029,0.9786,0.0051</t>
+  </si>
+  <si>
+    <t>0.3722,0.0414,0.6941,0.0197</t>
+  </si>
+  <si>
+    <t>0.2433,0.0223,0.8425,0.0118</t>
+  </si>
+  <si>
+    <t>0.4544,0.1826,0.3468,0.0132</t>
+  </si>
+  <si>
+    <t>0.3330,0.1668,0.3931,0.0032</t>
+  </si>
+  <si>
+    <t>0.2971,0.3342,0.4152,0.0194</t>
+  </si>
+  <si>
+    <t>0.4716,0.0624,0.6003,0.0128</t>
+  </si>
+  <si>
+    <t>0.3055,0.1082,0.6397,0.0335</t>
+  </si>
+  <si>
+    <t>0.5702,0.0369,0.4460,0.0334</t>
+  </si>
+  <si>
+    <t>0.9138,0.1182,0.0066,0.0068</t>
+  </si>
+  <si>
+    <t>0.9310,0.1052,0.0037,0.0075</t>
+  </si>
+  <si>
+    <t>0.8997,0.1622,0.0091,0.0053</t>
+  </si>
+  <si>
+    <t>0.9234,0.0749,0.0035,0.0237</t>
+  </si>
+  <si>
+    <t>0.9057,0.1495,0.0056,0.0076</t>
+  </si>
+  <si>
+    <t>0.5563,0.1523,0.3078,0.0180</t>
+  </si>
+  <si>
+    <t>0.7349,0.0454,0.1547,0.0594</t>
+  </si>
+  <si>
+    <t>0.7885,0.0161,0.1368,0.0369</t>
+  </si>
+  <si>
+    <t>0.6895,0.0410,0.2704,0.0277</t>
+  </si>
+  <si>
+    <t>0.6110,0.0122,0.4200,0.0418</t>
+  </si>
+  <si>
+    <t>0.0031,0.0026,0.9957,0.0033</t>
+  </si>
+  <si>
+    <t>0.0186,0.0273,0.9744,0.0057</t>
+  </si>
+  <si>
+    <t>0.0205,0.0328,0.9688,0.0091</t>
+  </si>
+  <si>
+    <t>0.0113,0.0474,0.9832,0.0020</t>
+  </si>
+  <si>
+    <t>0.0117,0.2399,0.9548,0.0027</t>
+  </si>
+  <si>
+    <t>0.9511,0.0060,0.0006,0.0563</t>
+  </si>
+  <si>
+    <t>0.9646,0.0083,0.0016,0.0271</t>
+  </si>
+  <si>
+    <t>0.9809,0.0068,0.0010,0.0137</t>
+  </si>
+  <si>
+    <t>0.9763,0.0085,0.0017,0.0142</t>
+  </si>
+  <si>
+    <t>0.9566,0.0089,0.0029,0.0367</t>
+  </si>
+  <si>
+    <t>0.9565,0.0095,0.0021,0.0389</t>
+  </si>
+  <si>
+    <t>0.9394,0.0042,0.0028,0.0689</t>
+  </si>
+  <si>
+    <t>0.9547,0.0095,0.0056,0.0316</t>
+  </si>
+  <si>
+    <t>0.0781,0.0162,0.9474,0.0102</t>
+  </si>
+  <si>
+    <t>0.3461,0.5918,0.1098,0.0154</t>
+  </si>
+  <si>
+    <t>0.8051,0.0110,0.2052,0.0276</t>
+  </si>
+  <si>
+    <t>0.0088,0.0018,0.9947,0.0007</t>
+  </si>
+  <si>
+    <t>0.0027,0.0067,0.9966,0.0011</t>
+  </si>
+  <si>
+    <t>0.0290,0.0149,0.9780,0.0017</t>
+  </si>
+  <si>
+    <t>0.0034,0.0053,0.9972,0.0004</t>
+  </si>
+  <si>
+    <t>0.1441,0.0403,0.8787,0.0086</t>
+  </si>
+  <si>
+    <t>0.0044,0.0051,0.9968,0.0005</t>
+  </si>
+  <si>
+    <t>0.0259,0.0149,0.9752,0.0033</t>
+  </si>
+  <si>
+    <t>0.3358,0.1762,0.4907,0.0190</t>
+  </si>
+  <si>
+    <t>0.4668,0.0265,0.5824,0.0346</t>
+  </si>
+  <si>
+    <t>0.6407,0.0205,0.3923,0.0197</t>
+  </si>
+  <si>
+    <t>0.8523,0.0270,0.0542,0.0317</t>
+  </si>
+  <si>
+    <t>0.9697,0.0267,0.0023,0.0095</t>
+  </si>
+  <si>
+    <t>0.9737,0.0086,0.0012,0.0209</t>
+  </si>
+  <si>
+    <t>0.9730,0.0203,0.0040,0.0101</t>
+  </si>
+  <si>
+    <t>0.9546,0.0118,0.0049,0.0269</t>
+  </si>
+  <si>
+    <t>0.9441,0.0165,0.0024,0.0482</t>
+  </si>
+  <si>
+    <t>0.9771,0.0124,0.0035,0.0090</t>
+  </si>
+  <si>
+    <t>0.9797,0.0112,0.0011,0.0109</t>
+  </si>
+  <si>
+    <t>0.9064,0.0074,0.0013,0.1189</t>
+  </si>
+  <si>
+    <t>0.1462,0.0465,0.8995,0.0029</t>
+  </si>
+  <si>
+    <t>0.0038,0.0348,0.9942,0.0006</t>
+  </si>
+  <si>
+    <t>0.0088,0.0058,0.9937,0.0005</t>
+  </si>
+  <si>
+    <t>0.1371,0.0257,0.9020,0.0081</t>
+  </si>
+  <si>
+    <t>0.0134,0.0018,0.9907,0.0019</t>
+  </si>
+  <si>
+    <t>0.0300,0.0061,0.8644,0.2710</t>
+  </si>
+  <si>
+    <t>0.2690,0.0275,0.8290,0.0123</t>
+  </si>
+  <si>
+    <t>0.0727,0.0598,0.9015,0.0301</t>
+  </si>
+  <si>
+    <t>0.0989,0.0025,0.0129,0.9193</t>
+  </si>
+  <si>
+    <t>0.0474,0.0135,0.0100,0.9678</t>
+  </si>
+  <si>
+    <t>0.0186,0.0012,0.0049,0.9846</t>
+  </si>
+  <si>
+    <t>0.0044,0.0005,0.0070,0.9929</t>
+  </si>
+  <si>
+    <t>0.0020,0.0005,0.0045,0.9959</t>
+  </si>
+  <si>
+    <t>0.5398,0.0212,0.0458,0.4482</t>
   </si>
 </sst>
 </file>
@@ -1953,10 +1962,10 @@
         <v>259</v>
       </c>
       <c r="C2" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1970,7 +1979,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,7 +1993,7 @@
         <v>260</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1998,7 +2007,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2021,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2035,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2049,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2063,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2077,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2091,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2105,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2119,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,7 +2133,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2138,7 +2147,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2149,10 +2158,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2166,7 +2175,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2177,10 +2186,10 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2203,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2217,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2222,7 +2231,7 @@
         <v>259</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2245,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2259,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2261,10 +2270,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,7 +2287,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2292,7 +2301,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2306,7 +2315,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2320,7 +2329,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2334,7 +2343,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2357,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,7 +2371,7 @@
         <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2376,7 +2385,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2399,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2404,7 +2413,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2427,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2429,10 +2438,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,7 +2455,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2460,7 +2469,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2471,10 +2480,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2488,7 +2497,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2502,7 +2511,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2516,7 +2525,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2530,7 +2539,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2553,7 @@
         <v>263</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2558,7 +2567,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2569,10 +2578,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2586,7 +2595,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2609,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2623,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,7 +2637,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,7 +2651,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2656,7 +2665,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2670,7 +2679,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2693,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2698,7 +2707,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2721,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2735,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2749,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2754,7 +2763,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2777,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2791,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2805,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,7 +2819,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,7 +2833,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,7 +2847,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2852,7 +2861,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2875,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,7 +2889,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2903,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,7 +2917,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2922,7 +2931,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,7 +2945,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2950,7 +2959,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2964,7 +2973,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,7 +2987,7 @@
         <v>263</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,7 +3001,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3006,7 +3015,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3020,7 +3029,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3034,7 +3043,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3048,7 +3057,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3062,7 +3071,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3076,7 +3085,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,7 +3099,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3101,10 +3110,10 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3115,10 +3124,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3132,7 +3141,7 @@
         <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,7 +3155,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,7 +3169,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3183,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3197,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3211,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3225,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3239,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3253,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3267,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3281,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3295,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3309,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3323,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3337,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3351,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3365,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3379,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3393,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3407,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3412,7 +3421,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,7 +3435,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3440,7 +3449,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3463,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3477,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3479,10 +3488,10 @@
         <v>262</v>
       </c>
       <c r="C111" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3493,10 +3502,10 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3519,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3533,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,7 +3547,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,7 +3561,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,7 +3575,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,7 +3589,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,7 +3603,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3605,10 +3614,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3631,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3645,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3650,7 +3659,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,7 +3673,7 @@
         <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3678,7 +3687,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,7 +3701,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,7 +3715,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3729,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3743,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3757,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3771,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3785,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3799,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3813,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3827,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,7 +3841,7 @@
         <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3846,7 +3855,7 @@
         <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,7 +3869,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,7 +3883,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,7 +3897,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,7 +3911,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,7 +3925,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,7 +3939,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3944,7 +3953,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3958,7 +3967,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3972,7 +3981,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3986,7 +3995,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,7 +4009,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4023,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4028,7 +4037,7 @@
         <v>259</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4051,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,7 +4065,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4079,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,7 +4093,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4107,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,7 +4121,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,7 +4135,7 @@
         <v>260</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4137,10 +4146,10 @@
         <v>259</v>
       </c>
       <c r="C158" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,7 +4163,7 @@
         <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4177,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4191,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4193,10 +4202,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,7 +4219,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4233,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4247,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4261,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4275,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4289,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4303,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4317,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4331,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4345,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,7 +4359,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,7 +4373,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4378,7 +4387,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4389,10 +4398,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4415,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4429,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4443,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4457,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4471,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4485,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4499,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4504,7 +4513,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4518,7 +4527,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,7 +4541,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4555,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4569,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4583,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4588,7 +4597,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4602,7 +4611,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4613,10 +4622,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4627,10 +4636,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4641,10 +4650,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,7 +4667,7 @@
         <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4669,10 +4678,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4683,10 +4692,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4700,7 +4709,7 @@
         <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4714,7 +4723,7 @@
         <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,7 +4737,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4751,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,7 +4765,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,7 +4779,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,7 +4793,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,7 +4807,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,7 +4821,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,7 +4835,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,7 +4849,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4854,7 +4863,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4868,7 +4877,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4882,7 +4891,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4896,7 +4905,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4919,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4933,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4947,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4961,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4975,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4989,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +5003,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5017,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5022,7 +5031,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5033,10 +5042,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5059,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5073,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5087,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5092,7 +5101,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5115,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5120,7 +5129,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5143,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5148,7 +5157,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5159,10 +5168,10 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,7 +5185,7 @@
         <v>261</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,7 +5199,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5213,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5227,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5241,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5255,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5269,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5283,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5297,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5311,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5325,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5330,7 +5339,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5344,7 +5353,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5358,7 +5367,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5372,7 +5381,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5395,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,7 +5409,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5414,7 +5423,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5428,7 +5437,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,7 +5451,7 @@
         <v>260</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5456,7 +5465,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5470,7 +5479,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5484,7 +5493,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5498,7 +5507,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,7 +5521,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
   </sheetData>
